--- a/R/df_weights.xlsx
+++ b/R/df_weights.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unhcr365-my.sharepoint.com/personal/jerabek_unhcr_org/Documents/UNHCR RBA Panama/CAM/JNA/Costa Rica/JNA_2024-main/R/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unhcr365-my.sharepoint.com/personal/jerabek_unhcr_org/Documents/UNHCR RBA Panama/CAM/PiN calculations - regional guidelines/JNA-2024-indicators-and-PiN-master/R/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="8_{BF3F6E6E-91F7-40BE-B6D9-9754F5A92DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC41A424-08A5-45BB-939D-3FE55670C28D}"/>
+  <xr:revisionPtr revIDLastSave="139" documentId="8_{4AA9007F-AF20-4BCF-A4D5-579C0C482D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05CD0F4F-5A86-4519-AA65-34A6394547CF}"/>
   <bookViews>
-    <workbookView xWindow="9825" yWindow="900" windowWidth="15375" windowHeight="14070" xr2:uid="{D2CAB68A-4BE7-4533-960F-AD53201F27A7}"/>
+    <workbookView xWindow="11262" yWindow="708" windowWidth="11136" windowHeight="11496" activeTab="1" xr2:uid="{D2CAB68A-4BE7-4533-960F-AD53201F27A7}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="in_destination" sheetId="1" r:id="rId1"/>
+    <sheet name="in_transit" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
   <si>
     <t>ind_weight_per_sector</t>
   </si>
@@ -111,6 +112,57 @@
   </si>
   <si>
     <t>IND_PRO_GBV_max</t>
+  </si>
+  <si>
+    <t>IND_HE</t>
+  </si>
+  <si>
+    <t>IND_FS</t>
+  </si>
+  <si>
+    <t>IND_WA_T1</t>
+  </si>
+  <si>
+    <t>IND_WA_T2</t>
+  </si>
+  <si>
+    <t>IND_WA_T3</t>
+  </si>
+  <si>
+    <t>IND_NUT_T1</t>
+  </si>
+  <si>
+    <t>IND_NUT_T2</t>
+  </si>
+  <si>
+    <t>IND_NUT_T3</t>
+  </si>
+  <si>
+    <t>IND_PRO_T1</t>
+  </si>
+  <si>
+    <t>IND_PRO_T2</t>
+  </si>
+  <si>
+    <t>IND_PRO_CP</t>
+  </si>
+  <si>
+    <t>IND_PRO_GBV</t>
+  </si>
+  <si>
+    <t>IND_HTS</t>
+  </si>
+  <si>
+    <t>IND_SHE_T1</t>
+  </si>
+  <si>
+    <t>IND_SHE_T2</t>
+  </si>
+  <si>
+    <t>IND_INT_T1</t>
+  </si>
+  <si>
+    <t>IND_EDU_T1</t>
   </si>
 </sst>
 </file>
@@ -154,10 +206,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -473,12 +526,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6BA0365-CD43-4A9D-A636-51BA1BB58BCC}">
   <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="2" width="18.625" customWidth="1"/>
+    <col min="1" max="2" width="18.6171875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -486,7 +539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>0.1111111111111111</v>
       </c>
@@ -494,7 +547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>0.11111111111111099</v>
       </c>
@@ -502,7 +555,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>0.1111111111111111</v>
       </c>
@@ -510,7 +563,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>3.7037037037037035E-2</v>
       </c>
@@ -518,7 +571,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>3.7037037037037035E-2</v>
       </c>
@@ -526,7 +579,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>3.7037037037037035E-2</v>
       </c>
@@ -534,7 +587,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>3.7037037037037035E-2</v>
       </c>
@@ -542,7 +595,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>3.7037037037037035E-2</v>
       </c>
@@ -550,7 +603,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>3.7037037037037035E-2</v>
       </c>
@@ -558,7 +611,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>2.0833333333333332E-2</v>
       </c>
@@ -566,7 +619,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>2.0833333333333332E-2</v>
       </c>
@@ -574,7 +627,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>1.3888888888888888E-2</v>
       </c>
@@ -582,7 +635,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>1.8518518518518517E-2</v>
       </c>
@@ -590,7 +643,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>1.8518518518518517E-2</v>
       </c>
@@ -598,7 +651,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>1.8518518518518517E-2</v>
       </c>
@@ -606,7 +659,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>3.7037037037037035E-2</v>
       </c>
@@ -614,7 +667,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>3.7037037037037035E-2</v>
       </c>
@@ -622,7 +675,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>3.7037037037037035E-2</v>
       </c>
@@ -630,7 +683,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>4.4444444444444446E-2</v>
       </c>
@@ -638,7 +691,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>4.4444444444444446E-2</v>
       </c>
@@ -646,7 +699,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>2.2222222222222223E-2</v>
       </c>
@@ -654,7 +707,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>5.5555555555555552E-2</v>
       </c>
@@ -662,7 +715,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>5.5555555555555552E-2</v>
       </c>
@@ -677,4 +730,190 @@
     <customPr name="layoutContexts" r:id="rId2"/>
   </customProperties>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45C19839-3382-483B-8912-81E99E331A73}">
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.76171875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" s="2">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" s="2">
+        <v>0.11764705882352929</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>2.8758169934640518E-2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>4.3572984749455326E-2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>4.3572984749455326E-2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>4.3572984749455326E-2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>2.8758169934640518E-2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>2.8758169934640518E-2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10">
+        <v>2.8758169934640518E-2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A11">
+        <v>2.8758169934640518E-2</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <v>8.0647058712418285E-2</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A13">
+        <v>4.3535947712418289E-2</v>
+      </c>
+      <c r="B13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A14">
+        <v>5.0980392156862737E-2</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A15">
+        <v>2.8758169934640518E-2</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A16">
+        <v>5.0980392156862737E-2</v>
+      </c>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="3"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A17" s="2">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="B17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="3"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A18" s="2">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="B18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A19" s="3"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B22" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <customProperties>
+    <customPr name="layoutContexts" r:id="rId1"/>
+    <customPr name="pages" r:id="rId2"/>
+    <customPr name="screen" r:id="rId3"/>
+  </customProperties>
+</worksheet>
 </file>